--- a/10-10-2026/PAT_Berth_Window.xlsx
+++ b/10-10-2026/PAT_Berth_Window.xlsx
@@ -251,6 +251,12 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -261,12 +267,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -924,7 +924,7 @@
       <c r="F9" s="45" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="30">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -962,7 +962,7 @@
       <c r="F10" s="45" t="n">
         <v>46309.25</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="30">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -1000,7 +1000,7 @@
       <c r="F11" s="45" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="30">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -1038,7 +1038,7 @@
       <c r="F12" s="45" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="30">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="F19" s="45" t="n">
         <v>46308.58333333334</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="30">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
@@ -1318,7 +1318,7 @@
       <c r="F20" s="45" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="30">
         <f>(F20-E20)*24</f>
         <v/>
       </c>

--- a/10-10-2026/PAT_Berth_Window.xlsx
+++ b/10-10-2026/PAT_Berth_Window.xlsx
@@ -251,22 +251,22 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -924,7 +924,7 @@
       <c r="F9" s="45" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="34">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -962,7 +962,7 @@
       <c r="F10" s="45" t="n">
         <v>46309.25</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="34">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -1000,7 +1000,7 @@
       <c r="F11" s="45" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="34">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -1038,7 +1038,7 @@
       <c r="F12" s="45" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="34">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1280,7 +1280,7 @@
       <c r="F19" s="45" t="n">
         <v>46308.58333333334</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="34">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
@@ -1318,7 +1318,7 @@
       <c r="F20" s="45" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="34">
         <f>(F20-E20)*24</f>
         <v/>
       </c>

--- a/10-10-2026/PAT_Berth_Window.xlsx
+++ b/10-10-2026/PAT_Berth_Window.xlsx
@@ -663,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -672,9 +672,10 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,15 +718,20 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Waiting for Berth (h)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Hours Alongside</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Shift</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Marked</t>
         </is>
@@ -755,15 +761,19 @@
         <v>46305.625</v>
       </c>
       <c r="G4" s="28">
+        <f>(E4-D4)*24</f>
+        <v/>
+      </c>
+      <c r="H4" s="28">
         <f>(F4-E4)*24</f>
         <v/>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr"/>
+      <c r="J4" s="23" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -789,15 +799,19 @@
         <v>46306.625</v>
       </c>
       <c r="G5" s="28">
+        <f>(E5-D5)*24</f>
+        <v/>
+      </c>
+      <c r="H5" s="28">
         <f>(F5-E5)*24</f>
         <v/>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr"/>
+      <c r="J5" s="23" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -823,15 +837,19 @@
         <v>46308.58333333334</v>
       </c>
       <c r="G6" s="28">
+        <f>(E6-D6)*24</f>
+        <v/>
+      </c>
+      <c r="H6" s="28">
         <f>(F6-E6)*24</f>
         <v/>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr"/>
+      <c r="J6" s="23" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -857,15 +875,19 @@
         <v>46309.29166666666</v>
       </c>
       <c r="G7" s="28">
+        <f>(E7-D7)*24</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
         <f>(F7-E7)*24</f>
         <v/>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>7B</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr"/>
+      <c r="J7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -891,15 +913,19 @@
         <v>46306.16666666666</v>
       </c>
       <c r="G8" s="28">
+        <f>(E8-D8)*24</f>
+        <v/>
+      </c>
+      <c r="H8" s="28">
         <f>(F8-E8)*24</f>
         <v/>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr"/>
+      <c r="J8" s="23" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -925,15 +951,19 @@
         <v>46307.08333333334</v>
       </c>
       <c r="G9" s="34">
+        <f>(E9-D9)*24</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -963,15 +993,19 @@
         <v>46309.25</v>
       </c>
       <c r="G10" s="34">
+        <f>(E10-D10)*24</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>1C</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1001,15 +1035,19 @@
         <v>46305.58333333334</v>
       </c>
       <c r="G11" s="34">
+        <f>(E11-D11)*24</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1039,15 +1077,19 @@
         <v>46307.08333333334</v>
       </c>
       <c r="G12" s="34">
+        <f>(E12-D12)*24</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="J12" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1077,15 +1119,19 @@
         <v>46309.625</v>
       </c>
       <c r="G13" s="28">
+        <f>(E13-D13)*24</f>
+        <v/>
+      </c>
+      <c r="H13" s="28">
         <f>(F13-E13)*24</f>
         <v/>
       </c>
-      <c r="H13" s="23" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr"/>
+      <c r="J13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1111,15 +1157,19 @@
         <v>46305.54166666666</v>
       </c>
       <c r="G14" s="28">
+        <f>(E14-D14)*24</f>
+        <v/>
+      </c>
+      <c r="H14" s="28">
         <f>(F14-E14)*24</f>
         <v/>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="I14" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I14" s="23" t="inlineStr"/>
+      <c r="J14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1145,15 +1195,19 @@
         <v>46306.25</v>
       </c>
       <c r="G15" s="28">
+        <f>(E15-D15)*24</f>
+        <v/>
+      </c>
+      <c r="H15" s="28">
         <f>(F15-E15)*24</f>
         <v/>
       </c>
-      <c r="H15" s="23" t="inlineStr">
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>4A</t>
         </is>
       </c>
-      <c r="I15" s="23" t="inlineStr"/>
+      <c r="J15" s="23" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1179,15 +1233,19 @@
         <v>46307.58333333334</v>
       </c>
       <c r="G16" s="28">
+        <f>(E16-D16)*24</f>
+        <v/>
+      </c>
+      <c r="H16" s="28">
         <f>(F16-E16)*24</f>
         <v/>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I16" s="23" t="inlineStr"/>
+      <c r="J16" s="23" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1213,15 +1271,19 @@
         <v>46309.20833333334</v>
       </c>
       <c r="G17" s="28">
+        <f>(E17-D17)*24</f>
+        <v/>
+      </c>
+      <c r="H17" s="28">
         <f>(F17-E17)*24</f>
         <v/>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr"/>
+      <c r="J17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1247,15 +1309,19 @@
         <v>46306.54166666666</v>
       </c>
       <c r="G18" s="28">
+        <f>(E18-D18)*24</f>
+        <v/>
+      </c>
+      <c r="H18" s="28">
         <f>(F18-E18)*24</f>
         <v/>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I18" s="23" t="inlineStr"/>
+      <c r="J18" s="23" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1281,15 +1347,19 @@
         <v>46308.58333333334</v>
       </c>
       <c r="G19" s="34">
+        <f>(E19-D19)*24</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1319,15 +1389,19 @@
         <v>46310.20833333334</v>
       </c>
       <c r="G20" s="34">
+        <f>(E20-D20)*24</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
         <f>(F20-E20)*24</f>
         <v/>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1369,7 +1443,8 @@
       </c>
       <c r="G24" s="40" t="n"/>
       <c r="H24" s="40" t="n"/>
-      <c r="I24" s="41" t="n"/>
+      <c r="I24" s="40" t="n"/>
+      <c r="J24" s="41" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -1396,7 +1471,8 @@
       </c>
       <c r="G25" s="40" t="n"/>
       <c r="H25" s="40" t="n"/>
-      <c r="I25" s="41" t="n"/>
+      <c r="I25" s="40" t="n"/>
+      <c r="J25" s="41" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
@@ -1423,13 +1499,14 @@
       </c>
       <c r="G26" s="40" t="n"/>
       <c r="H26" s="40" t="n"/>
-      <c r="I26" s="41" t="n"/>
+      <c r="I26" s="40" t="n"/>
+      <c r="J26" s="41" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="F26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/10-10-2026/PAT_Berth_Window.xlsx
+++ b/10-10-2026/PAT_Berth_Window.xlsx
@@ -171,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -223,22 +223,7 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,6 +233,9 @@
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -255,6 +243,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,17 +263,8 @@
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -293,9 +278,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -751,20 +733,20 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="44" t="n">
+      <c r="D4" s="39" t="n">
         <v>46303.66666666666</v>
       </c>
-      <c r="E4" s="44" t="n">
+      <c r="E4" s="39" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="F4" s="44" t="n">
+      <c r="F4" s="39" t="n">
         <v>46305.625</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="24">
         <f>(E4-D4)*24</f>
         <v/>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="24">
         <f>(F4-E4)*24</f>
         <v/>
       </c>
@@ -789,20 +771,20 @@
       <c r="C5" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D5" s="44" t="n">
+      <c r="D5" s="39" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="39" t="n">
         <v>46305.625</v>
       </c>
-      <c r="F5" s="44" t="n">
+      <c r="F5" s="39" t="n">
         <v>46306.625</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="24">
         <f>(E5-D5)*24</f>
         <v/>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="24">
         <f>(F5-E5)*24</f>
         <v/>
       </c>
@@ -827,20 +809,20 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="39" t="n">
         <v>46307.54166666666</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="39" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="39" t="n">
         <v>46308.58333333334</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="24">
         <f>(E6-D6)*24</f>
         <v/>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="24">
         <f>(F6-E6)*24</f>
         <v/>
       </c>
@@ -865,20 +847,20 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="39" t="n">
         <v>46308.29166666666</v>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="39" t="n">
         <v>46308.54166666666</v>
       </c>
-      <c r="F7" s="44" t="n">
+      <c r="F7" s="39" t="n">
         <v>46309.29166666666</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="24">
         <f>(E7-D7)*24</f>
         <v/>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="24">
         <f>(F7-E7)*24</f>
         <v/>
       </c>
@@ -903,20 +885,20 @@
       <c r="C8" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="39" t="n">
         <v>46304.25</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="39" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="F8" s="44" t="n">
+      <c r="F8" s="39" t="n">
         <v>46306.16666666666</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="24">
         <f>(E8-D8)*24</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="24">
         <f>(F8-E8)*24</f>
         <v/>
       </c>
@@ -941,20 +923,20 @@
       <c r="C9" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="40" t="n">
         <v>46305.875</v>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="40" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F9" s="45" t="n">
+      <c r="F9" s="40" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="32">
         <f>(E9-D9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="32">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -983,20 +965,20 @@
       <c r="C10" s="17" t="n">
         <v>537</v>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D10" s="40" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="40" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F10" s="45" t="n">
+      <c r="F10" s="40" t="n">
         <v>46309.25</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="32">
         <f>(E10-D10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="32">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -1025,20 +1007,20 @@
       <c r="C11" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="40" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="40" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="F11" s="45" t="n">
+      <c r="F11" s="40" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="32">
         <f>(E11-D11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="32">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -1067,20 +1049,20 @@
       <c r="C12" s="17" t="n">
         <v>565</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="40" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="40" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="F12" s="45" t="n">
+      <c r="F12" s="40" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="32">
         <f>(E12-D12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="32">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1109,20 +1091,20 @@
       <c r="C13" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="39" t="n">
         <v>46307.95833333334</v>
       </c>
-      <c r="E13" s="44" t="n">
+      <c r="E13" s="39" t="n">
         <v>46308.20833333334</v>
       </c>
-      <c r="F13" s="44" t="n">
+      <c r="F13" s="39" t="n">
         <v>46309.625</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="24">
         <f>(E13-D13)*24</f>
         <v/>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="24">
         <f>(F13-E13)*24</f>
         <v/>
       </c>
@@ -1147,20 +1129,20 @@
       <c r="C14" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="39" t="n">
         <v>46304</v>
       </c>
-      <c r="E14" s="44" t="n">
+      <c r="E14" s="39" t="n">
         <v>46304</v>
       </c>
-      <c r="F14" s="44" t="n">
+      <c r="F14" s="39" t="n">
         <v>46305.54166666666</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="24">
         <f>(E14-D14)*24</f>
         <v/>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="24">
         <f>(F14-E14)*24</f>
         <v/>
       </c>
@@ -1185,20 +1167,20 @@
       <c r="C15" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="39" t="n">
         <v>46304.83333333334</v>
       </c>
-      <c r="E15" s="44" t="n">
+      <c r="E15" s="39" t="n">
         <v>46305.66666666666</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="39" t="n">
         <v>46306.25</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="24">
         <f>(E15-D15)*24</f>
         <v/>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="24">
         <f>(F15-E15)*24</f>
         <v/>
       </c>
@@ -1223,20 +1205,20 @@
       <c r="C16" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D16" s="44" t="n">
+      <c r="D16" s="39" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E16" s="44" t="n">
+      <c r="E16" s="39" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="39" t="n">
         <v>46307.58333333334</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="24">
         <f>(E16-D16)*24</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="24">
         <f>(F16-E16)*24</f>
         <v/>
       </c>
@@ -1261,20 +1243,20 @@
       <c r="C17" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="39" t="n">
         <v>46307.375</v>
       </c>
-      <c r="E17" s="44" t="n">
+      <c r="E17" s="39" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="39" t="n">
         <v>46309.20833333334</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="24">
         <f>(E17-D17)*24</f>
         <v/>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="24">
         <f>(F17-E17)*24</f>
         <v/>
       </c>
@@ -1299,20 +1281,20 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="39" t="n">
         <v>46302.83333333334</v>
       </c>
-      <c r="E18" s="44" t="n">
+      <c r="E18" s="39" t="n">
         <v>46304.625</v>
       </c>
-      <c r="F18" s="44" t="n">
+      <c r="F18" s="39" t="n">
         <v>46306.54166666666</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="24">
         <f>(E18-D18)*24</f>
         <v/>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="24">
         <f>(F18-E18)*24</f>
         <v/>
       </c>
@@ -1337,20 +1319,20 @@
       <c r="C19" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="45" t="n">
+      <c r="D19" s="40" t="n">
         <v>46307.04166666666</v>
       </c>
-      <c r="E19" s="45" t="n">
+      <c r="E19" s="40" t="n">
         <v>46307.25</v>
       </c>
-      <c r="F19" s="45" t="n">
+      <c r="F19" s="40" t="n">
         <v>46308.58333333334</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="32">
         <f>(E19-D19)*24</f>
         <v/>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="32">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
@@ -1379,20 +1361,20 @@
       <c r="C20" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D20" s="40" t="n">
         <v>46308.16666666666</v>
       </c>
-      <c r="E20" s="45" t="n">
+      <c r="E20" s="40" t="n">
         <v>46308.66666666666</v>
       </c>
-      <c r="F20" s="45" t="n">
+      <c r="F20" s="40" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="32">
         <f>(E20-D20)*24</f>
         <v/>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="32">
         <f>(F20-E20)*24</f>
         <v/>
       </c>
@@ -1408,7 +1390,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1441,10 +1423,10 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G24" s="40" t="n"/>
-      <c r="H24" s="40" t="n"/>
-      <c r="I24" s="40" t="n"/>
-      <c r="J24" s="41" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="36" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -1457,11 +1439,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C25" s="43" t="n"/>
-      <c r="D25" s="46" t="n">
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="41" t="n">
         <v>46299</v>
       </c>
-      <c r="E25" s="46" t="n">
+      <c r="E25" s="41" t="n">
         <v>46319</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -1469,38 +1451,38 @@
           <t>Close on 4–24 Oct 2026 to renovate electric channel (HE JIN is alongside at 20D; other vessels are booked from 10/16)  —  Unchanged – conflicts with vessel bookings, please confirm</t>
         </is>
       </c>
-      <c r="G25" s="40" t="n"/>
-      <c r="H25" s="40" t="n"/>
-      <c r="I25" s="40" t="n"/>
-      <c r="J25" s="41" t="n"/>
+      <c r="G25" s="35" t="n"/>
+      <c r="H25" s="35" t="n"/>
+      <c r="I25" s="35" t="n"/>
+      <c r="J25" s="36" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>20E / G.25</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t>Gate stopped</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n"/>
-      <c r="D26" s="47" t="n">
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="41" t="n">
         <v>46300</v>
       </c>
-      <c r="E26" s="47" t="n">
+      <c r="E26" s="41" t="n">
         <v>46313</v>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>G.25 stops working 5–18 Oct 2026 to change trolley rail (in progress)  —  Unchanged</t>
         </is>
       </c>
-      <c r="G26" s="40" t="n"/>
-      <c r="H26" s="40" t="n"/>
-      <c r="I26" s="40" t="n"/>
-      <c r="J26" s="41" t="n"/>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+      <c r="I26" s="35" t="n"/>
+      <c r="J26" s="36" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/10-10-2026/PAT_Berth_Window.xlsx
+++ b/10-10-2026/PAT_Berth_Window.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="166" formatCode="[$-409]dd-mmm-yyyy hh:mm"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,11 @@
       <b val="1"/>
       <color rgb="0016324F"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -171,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,7 +235,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -248,29 +253,30 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -733,13 +739,13 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="39" t="n">
+      <c r="D4" s="40" t="n">
         <v>46303.66666666666</v>
       </c>
-      <c r="E4" s="39" t="n">
+      <c r="E4" s="40" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F4" s="40" t="n">
         <v>46305.625</v>
       </c>
       <c r="G4" s="24">
@@ -771,13 +777,13 @@
       <c r="C5" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="40" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="40" t="n">
         <v>46305.625</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="40" t="n">
         <v>46306.625</v>
       </c>
       <c r="G5" s="24">
@@ -809,13 +815,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="40" t="n">
         <v>46307.54166666666</v>
       </c>
-      <c r="E6" s="39" t="n">
+      <c r="E6" s="40" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="40" t="n">
         <v>46308.58333333334</v>
       </c>
       <c r="G6" s="24">
@@ -847,13 +853,13 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="40" t="n">
         <v>46308.29166666666</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="40" t="n">
         <v>46308.54166666666</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="40" t="n">
         <v>46309.29166666666</v>
       </c>
       <c r="G7" s="24">
@@ -885,13 +891,13 @@
       <c r="C8" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="40" t="n">
         <v>46304.25</v>
       </c>
-      <c r="E8" s="39" t="n">
+      <c r="E8" s="40" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="40" t="n">
         <v>46306.16666666666</v>
       </c>
       <c r="G8" s="24">
@@ -923,20 +929,20 @@
       <c r="C9" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="41" t="n">
         <v>46305.875</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="41" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="41" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G9" s="32">
+      <c r="G9" s="33">
         <f>(E9-D9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="33">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -965,20 +971,20 @@
       <c r="C10" s="17" t="n">
         <v>537</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="41" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="41" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="41" t="n">
         <v>46309.25</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="33">
         <f>(E10-D10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="33">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -1007,20 +1013,20 @@
       <c r="C11" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="41" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="41" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="41" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="33">
         <f>(E11-D11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="33">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -1049,20 +1055,20 @@
       <c r="C12" s="17" t="n">
         <v>565</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="41" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="41" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="41" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="33">
         <f>(E12-D12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="33">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1091,13 +1097,13 @@
       <c r="C13" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D13" s="40" t="n">
         <v>46307.95833333334</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="40" t="n">
         <v>46308.20833333334</v>
       </c>
-      <c r="F13" s="39" t="n">
+      <c r="F13" s="40" t="n">
         <v>46309.625</v>
       </c>
       <c r="G13" s="24">
@@ -1129,13 +1135,13 @@
       <c r="C14" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D14" s="40" t="n">
         <v>46304</v>
       </c>
-      <c r="E14" s="39" t="n">
+      <c r="E14" s="40" t="n">
         <v>46304</v>
       </c>
-      <c r="F14" s="39" t="n">
+      <c r="F14" s="40" t="n">
         <v>46305.54166666666</v>
       </c>
       <c r="G14" s="24">
@@ -1167,13 +1173,13 @@
       <c r="C15" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D15" s="40" t="n">
         <v>46304.83333333334</v>
       </c>
-      <c r="E15" s="39" t="n">
+      <c r="E15" s="40" t="n">
         <v>46305.66666666666</v>
       </c>
-      <c r="F15" s="39" t="n">
+      <c r="F15" s="40" t="n">
         <v>46306.25</v>
       </c>
       <c r="G15" s="24">
@@ -1205,13 +1211,13 @@
       <c r="C16" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D16" s="40" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E16" s="39" t="n">
+      <c r="E16" s="40" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F16" s="39" t="n">
+      <c r="F16" s="40" t="n">
         <v>46307.58333333334</v>
       </c>
       <c r="G16" s="24">
@@ -1243,13 +1249,13 @@
       <c r="C17" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D17" s="40" t="n">
         <v>46307.375</v>
       </c>
-      <c r="E17" s="39" t="n">
+      <c r="E17" s="40" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F17" s="40" t="n">
         <v>46309.20833333334</v>
       </c>
       <c r="G17" s="24">
@@ -1281,13 +1287,13 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D18" s="40" t="n">
         <v>46302.83333333334</v>
       </c>
-      <c r="E18" s="39" t="n">
+      <c r="E18" s="40" t="n">
         <v>46304.625</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="40" t="n">
         <v>46306.54166666666</v>
       </c>
       <c r="G18" s="24">
@@ -1319,20 +1325,20 @@
       <c r="C19" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="40" t="n">
+      <c r="D19" s="41" t="n">
         <v>46307.04166666666</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E19" s="41" t="n">
         <v>46307.25</v>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="41" t="n">
         <v>46308.58333333334</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="33">
         <f>(E19-D19)*24</f>
         <v/>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="33">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
@@ -1361,20 +1367,20 @@
       <c r="C20" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="41" t="n">
         <v>46308.16666666666</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E20" s="41" t="n">
         <v>46308.66666666666</v>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="41" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="33">
         <f>(E20-D20)*24</f>
         <v/>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="33">
         <f>(F20-E20)*24</f>
         <v/>
       </c>
@@ -1440,10 +1446,10 @@
         </is>
       </c>
       <c r="C25" s="38" t="n"/>
-      <c r="D25" s="41" t="n">
+      <c r="D25" s="42" t="n">
         <v>46299</v>
       </c>
-      <c r="E25" s="41" t="n">
+      <c r="E25" s="42" t="n">
         <v>46319</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -1468,10 +1474,10 @@
         </is>
       </c>
       <c r="C26" s="38" t="n"/>
-      <c r="D26" s="41" t="n">
+      <c r="D26" s="42" t="n">
         <v>46300</v>
       </c>
-      <c r="E26" s="41" t="n">
+      <c r="E26" s="42" t="n">
         <v>46313</v>
       </c>
       <c r="F26" s="16" t="inlineStr">

--- a/10-10-2026/PAT_Berth_Window.xlsx
+++ b/10-10-2026/PAT_Berth_Window.xlsx
@@ -244,6 +244,12 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -264,12 +270,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -938,11 +938,11 @@
       <c r="F9" s="41" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="26">
         <f>(E9-D9)*24</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="26">
         <f>(F9-E9)*24</f>
         <v/>
       </c>
@@ -980,11 +980,11 @@
       <c r="F10" s="41" t="n">
         <v>46309.25</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="26">
         <f>(E10-D10)*24</f>
         <v/>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="26">
         <f>(F10-E10)*24</f>
         <v/>
       </c>
@@ -1022,11 +1022,11 @@
       <c r="F11" s="41" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="G11" s="33">
+      <c r="G11" s="26">
         <f>(E11-D11)*24</f>
         <v/>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="26">
         <f>(F11-E11)*24</f>
         <v/>
       </c>
@@ -1064,11 +1064,11 @@
       <c r="F12" s="41" t="n">
         <v>46307.08333333334</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="26">
         <f>(E12-D12)*24</f>
         <v/>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="26">
         <f>(F12-E12)*24</f>
         <v/>
       </c>
@@ -1334,11 +1334,11 @@
       <c r="F19" s="41" t="n">
         <v>46308.58333333334</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="26">
         <f>(E19-D19)*24</f>
         <v/>
       </c>
-      <c r="H19" s="33">
+      <c r="H19" s="26">
         <f>(F19-E19)*24</f>
         <v/>
       </c>
@@ -1376,11 +1376,11 @@
       <c r="F20" s="41" t="n">
         <v>46310.20833333334</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="26">
         <f>(E20-D20)*24</f>
         <v/>
       </c>
-      <c r="H20" s="33">
+      <c r="H20" s="26">
         <f>(F20-E20)*24</f>
         <v/>
       </c>

--- a/10-10-2026/PAT_Berth_Window.xlsx
+++ b/10-10-2026/PAT_Berth_Window.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +270,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -739,13 +748,13 @@
       <c r="C4" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="43" t="n">
         <v>46303.66666666666</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="43" t="n">
         <v>46304.58333333334</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="43" t="n">
         <v>46305.625</v>
       </c>
       <c r="G4" s="24">
@@ -777,13 +786,13 @@
       <c r="C5" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="43" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="43" t="n">
         <v>46305.625</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="43" t="n">
         <v>46306.625</v>
       </c>
       <c r="G5" s="24">
@@ -815,13 +824,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="43" t="n">
         <v>46307.54166666666</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="43" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="43" t="n">
         <v>46308.58333333334</v>
       </c>
       <c r="G6" s="24">
@@ -853,13 +862,13 @@
       <c r="C7" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="43" t="n">
         <v>46308.29166666666</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="43" t="n">
         <v>46308.54166666666</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="43" t="n">
         <v>46309.29166666666</v>
       </c>
       <c r="G7" s="24">
@@ -891,13 +900,13 @@
       <c r="C8" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="43" t="n">
         <v>46304.25</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="43" t="n">
         <v>46304.66666666666</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="43" t="n">
         <v>46306.16666666666</v>
       </c>
       <c r="G8" s="24">
@@ -929,13 +938,13 @@
       <c r="C9" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="44" t="n">
         <v>46305.875</v>
       </c>
-      <c r="E9" s="41" t="n">
+      <c r="E9" s="44" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F9" s="44" t="n">
         <v>46307.08333333334</v>
       </c>
       <c r="G9" s="26">
@@ -971,13 +980,13 @@
       <c r="C10" s="17" t="n">
         <v>537</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="44" t="n">
         <v>46307.91666666666</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="44" t="n">
         <v>46308.25</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="44" t="n">
         <v>46309.25</v>
       </c>
       <c r="G10" s="26">
@@ -1013,13 +1022,13 @@
       <c r="C11" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D11" s="41" t="n">
+      <c r="D11" s="44" t="n">
         <v>46303.54166666666</v>
       </c>
-      <c r="E11" s="41" t="n">
+      <c r="E11" s="44" t="n">
         <v>46304.54166666666</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F11" s="44" t="n">
         <v>46305.58333333334</v>
       </c>
       <c r="G11" s="26">
@@ -1055,13 +1064,13 @@
       <c r="C12" s="17" t="n">
         <v>565</v>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D12" s="44" t="n">
         <v>46304.91666666666</v>
       </c>
-      <c r="E12" s="41" t="n">
+      <c r="E12" s="44" t="n">
         <v>46305.58333333334</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="44" t="n">
         <v>46307.08333333334</v>
       </c>
       <c r="G12" s="26">
@@ -1097,13 +1106,13 @@
       <c r="C13" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="43" t="n">
         <v>46307.95833333334</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="43" t="n">
         <v>46308.20833333334</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="43" t="n">
         <v>46309.625</v>
       </c>
       <c r="G13" s="24">
@@ -1135,13 +1144,13 @@
       <c r="C14" s="23" t="n">
         <v>552</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="43" t="n">
         <v>46304</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E14" s="43" t="n">
         <v>46304</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="43" t="n">
         <v>46305.54166666666</v>
       </c>
       <c r="G14" s="24">
@@ -1173,13 +1182,13 @@
       <c r="C15" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="43" t="n">
         <v>46304.83333333334</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="43" t="n">
         <v>46305.66666666666</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="43" t="n">
         <v>46306.25</v>
       </c>
       <c r="G15" s="24">
@@ -1211,13 +1220,13 @@
       <c r="C16" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="43" t="n">
         <v>46305.70833333334</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E16" s="43" t="n">
         <v>46306.20833333334</v>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="43" t="n">
         <v>46307.58333333334</v>
       </c>
       <c r="G16" s="24">
@@ -1249,13 +1258,13 @@
       <c r="C17" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="43" t="n">
         <v>46307.375</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E17" s="43" t="n">
         <v>46307.66666666666</v>
       </c>
-      <c r="F17" s="40" t="n">
+      <c r="F17" s="43" t="n">
         <v>46309.20833333334</v>
       </c>
       <c r="G17" s="24">
@@ -1287,13 +1296,13 @@
       <c r="C18" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D18" s="43" t="n">
         <v>46302.83333333334</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E18" s="43" t="n">
         <v>46304.625</v>
       </c>
-      <c r="F18" s="40" t="n">
+      <c r="F18" s="43" t="n">
         <v>46306.54166666666</v>
       </c>
       <c r="G18" s="24">
@@ -1325,13 +1334,13 @@
       <c r="C19" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D19" s="41" t="n">
+      <c r="D19" s="44" t="n">
         <v>46307.04166666666</v>
       </c>
-      <c r="E19" s="41" t="n">
+      <c r="E19" s="44" t="n">
         <v>46307.25</v>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F19" s="44" t="n">
         <v>46308.58333333334</v>
       </c>
       <c r="G19" s="26">
@@ -1367,13 +1376,13 @@
       <c r="C20" s="17" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="41" t="n">
+      <c r="D20" s="44" t="n">
         <v>46308.16666666666</v>
       </c>
-      <c r="E20" s="41" t="n">
+      <c r="E20" s="44" t="n">
         <v>46308.66666666666</v>
       </c>
-      <c r="F20" s="41" t="n">
+      <c r="F20" s="44" t="n">
         <v>46310.20833333334</v>
       </c>
       <c r="G20" s="26">
@@ -1396,7 +1405,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1429,10 +1438,10 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
-      <c r="J24" s="36" t="n"/>
+      <c r="G24" s="38" t="n"/>
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="38" t="n"/>
+      <c r="J24" s="39" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -1445,11 +1454,11 @@
           <t>Berth closed</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="42" t="n">
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="45" t="n">
         <v>46299</v>
       </c>
-      <c r="E25" s="42" t="n">
+      <c r="E25" s="45" t="n">
         <v>46319</v>
       </c>
       <c r="F25" s="16" t="inlineStr">
@@ -1457,10 +1466,10 @@
           <t>Close on 4–24 Oct 2026 to renovate electric channel (HE JIN is alongside at 20D; other vessels are booked from 10/16)  —  Unchanged – conflicts with vessel bookings, please confirm</t>
         </is>
       </c>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
-      <c r="J25" s="36" t="n"/>
+      <c r="G25" s="38" t="n"/>
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="39" t="n"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -1473,11 +1482,11 @@
           <t>Gate stopped</t>
         </is>
       </c>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="42" t="n">
+      <c r="C26" s="41" t="n"/>
+      <c r="D26" s="45" t="n">
         <v>46300</v>
       </c>
-      <c r="E26" s="42" t="n">
+      <c r="E26" s="45" t="n">
         <v>46313</v>
       </c>
       <c r="F26" s="16" t="inlineStr">
@@ -1485,10 +1494,10 @@
           <t>G.25 stops working 5–18 Oct 2026 to change trolley rail (in progress)  —  Unchanged</t>
         </is>
       </c>
-      <c r="G26" s="35" t="n"/>
-      <c r="H26" s="35" t="n"/>
-      <c r="I26" s="35" t="n"/>
-      <c r="J26" s="36" t="n"/>
+      <c r="G26" s="38" t="n"/>
+      <c r="H26" s="38" t="n"/>
+      <c r="I26" s="38" t="n"/>
+      <c r="J26" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
